--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>879</v>
+        <v>874</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>874</v>
+        <v>777</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>777</v>
+        <v>754</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>754</v>
+        <v>760</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>760</v>
+        <v>875</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>875</v>
+        <v>866</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>866</v>
+        <v>1056</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1056</v>
+        <v>1086</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1086</v>
+        <v>1092</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1092</v>
+        <v>1099</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1099</v>
+        <v>1100</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1100</v>
+        <v>1058</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1058</v>
+        <v>1215</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1215</v>
+        <v>1214</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1214</v>
+        <v>1111</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1111</v>
+        <v>1104</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1104</v>
+        <v>1115</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1115</v>
+        <v>1122</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1122</v>
+        <v>1152</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1152</v>
+        <v>1225</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1225</v>
+        <v>1350</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1350</v>
+        <v>1352</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1352</v>
+        <v>1356</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1356</v>
+        <v>1367</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1367</v>
+        <v>1096</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1096</v>
+        <v>1034</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1034</v>
+        <v>1066</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1066</v>
+        <v>1006</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1006</v>
+        <v>991</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>991</v>
+        <v>1051</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1051</v>
+        <v>1075</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1075</v>
+        <v>1052</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1052</v>
+        <v>1007</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1007</v>
+        <v>1086</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1086</v>
+        <v>1084</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1084</v>
+        <v>951</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>951</v>
+        <v>760</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>760</v>
+        <v>729</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>729</v>
+        <v>699</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>699</v>
+        <v>687</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>687</v>
+        <v>564</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>563</v>
+        <v>531</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>531</v>
+        <v>586</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>586</v>
+        <v>636</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>636</v>
+        <v>632</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>632</v>
+        <v>628</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>628</v>
+        <v>638</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>638</v>
+        <v>641</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>641</v>
+        <v>693</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>693</v>
+        <v>915</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>915</v>
+        <v>959</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>959</v>
+        <v>1034</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1034</v>
+        <v>1028</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1028</v>
+        <v>1064</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1064</v>
+        <v>931</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>931</v>
+        <v>873</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>873</v>
+        <v>853</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>853</v>
+        <v>867</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>866</v>
+        <v>779</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>779</v>
+        <v>824</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>824</v>
+        <v>913</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>913</v>
+        <v>1004</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1004</v>
+        <v>962</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>962</v>
+        <v>1001</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1001</v>
+        <v>1013</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>1013</v>
+        <v>985</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>985</v>
+        <v>825</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>825</v>
+        <v>776</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>776</v>
+        <v>766</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>766</v>
+        <v>749</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>749</v>
+        <v>722</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>722</v>
+        <v>687</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>687</v>
+        <v>664</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>664</v>
+        <v>675</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>675</v>
+        <v>682</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>682</v>
+        <v>693</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>693</v>
+        <v>670</v>
       </c>
     </row>
   </sheetData>

--- a/output/velo-pl.xlsx
+++ b/output/velo-pl.xlsx
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>670</v>
+        <v>580</v>
       </c>
     </row>
   </sheetData>
